--- a/paridade_36.xlsx
+++ b/paridade_36.xlsx
@@ -3359,7 +3359,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>T4 Média Todas &gt;= 7.21</t>
+          <t>T4 Média Todas &gt;= 7.18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3424,7 +3424,7 @@
         <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>7.21</v>
+        <v>7.18</v>
       </c>
       <c r="Z38" t="inlineStr"/>
       <c r="AA38" t="inlineStr"/>
@@ -3435,7 +3435,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>T4 Média Todas &lt;= 6.47</t>
+          <t>T4 Média Todas &lt;= 6.45</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="Y39" t="inlineStr"/>
       <c r="Z39" t="n">
-        <v>6.47</v>
+        <v>6.45</v>
       </c>
       <c r="AA39" t="inlineStr"/>
       <c r="AB39" t="inlineStr"/>
@@ -3511,7 +3511,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>T4 Gap Todas &gt;= -0.55</t>
+          <t>T4 Gap Todas &gt;= -0.56</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3576,7 +3576,7 @@
         <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>-0.55</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="Z40" t="inlineStr"/>
       <c r="AA40" t="inlineStr"/>
@@ -3587,7 +3587,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>T4 Gap Todas &lt;= -1.72</t>
+          <t>T4 Gap Todas &lt;= -1.74</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="Y41" t="inlineStr"/>
       <c r="Z41" t="n">
-        <v>-1.72</v>
+        <v>-1.74</v>
       </c>
       <c r="AA41" t="inlineStr"/>
       <c r="AB41" t="inlineStr"/>
@@ -3739,7 +3739,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>T4 Z Todas &lt;= -0.23</t>
+          <t>T4 Z Todas &lt;= -0.22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="Y43" t="inlineStr"/>
       <c r="Z43" t="n">
-        <v>-0.23</v>
+        <v>-0.22</v>
       </c>
       <c r="AA43" t="inlineStr"/>
       <c r="AB43" t="inlineStr"/>
@@ -3815,7 +3815,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>T4 Média Últ. 5 &gt;= 7.8</t>
+          <t>T4 Média Últ. 5 &gt;= 7.6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3880,7 +3880,7 @@
         <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="Z44" t="inlineStr"/>
       <c r="AA44" t="inlineStr"/>
@@ -3967,7 +3967,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>T4 Gap Últ. 5 &gt;= -0.1</t>
+          <t>T4 Gap Últ. 5 &gt;= 0.1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4032,7 +4032,7 @@
         <v>5</v>
       </c>
       <c r="Y46" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="Z46" t="inlineStr"/>
       <c r="AA46" t="inlineStr"/>
@@ -4119,7 +4119,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>T4 Z Últ. 5 &gt;= 0.03</t>
+          <t>T4 Z Últ. 5 &gt;= -0.03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4184,7 +4184,7 @@
         <v>5</v>
       </c>
       <c r="Y48" t="n">
-        <v>0.03</v>
+        <v>-0.03</v>
       </c>
       <c r="Z48" t="inlineStr"/>
       <c r="AA48" t="inlineStr"/>
@@ -5183,7 +5183,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>T4 Média Últ. 20 &gt;= 7.7</t>
+          <t>T4 Média Últ. 20 &gt;= 7.67</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -5248,7 +5248,7 @@
         <v>20</v>
       </c>
       <c r="Y62" t="n">
-        <v>7.7</v>
+        <v>7.67</v>
       </c>
       <c r="Z62" t="inlineStr"/>
       <c r="AA62" t="inlineStr"/>
@@ -5411,7 +5411,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>T4 Gap Últ. 20 &lt;= -1.17</t>
+          <t>T4 Gap Últ. 20 &lt;= -1.15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="Y65" t="inlineStr"/>
       <c r="Z65" t="n">
-        <v>-1.17</v>
+        <v>-1.15</v>
       </c>
       <c r="AA65" t="inlineStr"/>
       <c r="AB65" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>T4 Média Últ. 30 &gt;= 7.63</t>
+          <t>T4 Média Últ. 30 &gt;= 7.6</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5704,7 +5704,7 @@
         <v>30</v>
       </c>
       <c r="Y68" t="n">
-        <v>7.63</v>
+        <v>7.6</v>
       </c>
       <c r="Z68" t="inlineStr"/>
       <c r="AA68" t="inlineStr"/>
@@ -5867,7 +5867,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>T4 Gap Últ. 30 &lt;= -1.23</t>
+          <t>T4 Gap Últ. 30 &lt;= -1.2</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="Y71" t="inlineStr"/>
       <c r="Z71" t="n">
-        <v>-1.23</v>
+        <v>-1.2</v>
       </c>
       <c r="AA71" t="inlineStr"/>
       <c r="AB71" t="inlineStr"/>
@@ -6171,7 +6171,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>T4 Média Últ. 50 &lt;= 6.74</t>
+          <t>T4 Média Últ. 50 &lt;= 6.76</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="Y75" t="inlineStr"/>
       <c r="Z75" t="n">
-        <v>6.74</v>
+        <v>6.76</v>
       </c>
       <c r="AA75" t="inlineStr"/>
       <c r="AB75" t="inlineStr"/>
@@ -6247,7 +6247,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>T4 Gap Últ. 50 &gt;= -0.18</t>
+          <t>T4 Gap Últ. 50 &gt;= -0.19</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -6312,7 +6312,7 @@
         <v>50</v>
       </c>
       <c r="Y76" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
       <c r="Z76" t="inlineStr"/>
       <c r="AA76" t="inlineStr"/>
@@ -6323,7 +6323,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>T4 Gap Últ. 50 &lt;= -1.36</t>
+          <t>T4 Gap Últ. 50 &lt;= -1.34</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -6389,7 +6389,7 @@
       </c>
       <c r="Y77" t="inlineStr"/>
       <c r="Z77" t="n">
-        <v>-1.36</v>
+        <v>-1.34</v>
       </c>
       <c r="AA77" t="inlineStr"/>
       <c r="AB77" t="inlineStr"/>
@@ -6475,7 +6475,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>T4 Z Últ. 50 &lt;= -0.37</t>
+          <t>T4 Z Últ. 50 &lt;= -0.36</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="Y79" t="inlineStr"/>
       <c r="Z79" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="AA79" t="inlineStr"/>
       <c r="AB79" t="inlineStr"/>
@@ -6551,7 +6551,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>T4 Tendência &gt;= 0</t>
+          <t>T4 Tendência &gt;= 0.05</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -6616,7 +6616,7 @@
         <v>0</v>
       </c>
       <c r="Y80" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="Z80" t="inlineStr"/>
       <c r="AA80" t="inlineStr"/>
@@ -6627,7 +6627,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>T4 Tendência &lt;= -0.45</t>
+          <t>T4 Tendência &lt;= -0.5</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="Y81" t="inlineStr"/>
       <c r="Z81" t="n">
-        <v>-0.45</v>
+        <v>-0.5</v>
       </c>
       <c r="AA81" t="inlineStr"/>
       <c r="AB81" t="inlineStr"/>
